--- a/Интеллектуальный анализ данных/Лабораторные работы/ЛР2/ExpData.xlsx
+++ b/Интеллектуальный анализ данных/Лабораторные работы/ЛР2/ExpData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\6 семестр\Интеллектуальный анализ данных\Лабораторные работы\ЛР2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Honor\OneDrive\Рабочий стол\Lessons\Интеллектуальный анализ данных\Лабораторные работы\ЛР2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4258E7A-18A5-4A92-8050-27E5952922CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0608CD-0832-4E94-9065-9191ADEF745B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -162,12 +162,6 @@
     <t>Мали</t>
   </si>
   <si>
-    <t>Безработица 15-24 (%)</t>
-  </si>
-  <si>
-    <t>Безработица 25-54 (%)</t>
-  </si>
-  <si>
     <t>ИПЦ (0-100)</t>
   </si>
   <si>
@@ -177,7 +171,13 @@
     <t>Инфляция (%)</t>
   </si>
   <si>
-    <t>Убийства (всего)</t>
+    <t>Количество людей за чертой бедности</t>
+  </si>
+  <si>
+    <t>Отношение Широкой денежной массы к ВВП</t>
+  </si>
+  <si>
+    <t>Продолжительность жизни</t>
   </si>
 </sst>
 </file>
@@ -545,49 +545,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="17.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
-        <v>26.170999999999999</v>
-      </c>
-      <c r="C2" s="2">
-        <v>4.9809999999999999</v>
-      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
       <c r="D2" s="3">
         <v>40</v>
       </c>
@@ -597,20 +593,14 @@
       <c r="F2" s="2">
         <v>4.8099999999999996</v>
       </c>
-      <c r="G2" s="2">
-        <v>45472.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
-        <v>14.92</v>
-      </c>
-      <c r="C3" s="2">
-        <v>7.1139999999999999</v>
-      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
       <c r="D3" s="3">
         <v>67</v>
       </c>
@@ -620,20 +610,14 @@
       <c r="F3" s="2">
         <v>4.38</v>
       </c>
-      <c r="G3" s="2">
-        <v>25002.799999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
-        <v>14.798999999999999</v>
-      </c>
-      <c r="C4" s="2">
-        <v>2.8079999999999998</v>
-      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
       <c r="D4" s="3">
         <v>38</v>
       </c>
@@ -643,20 +627,14 @@
       <c r="F4" s="2">
         <v>1.6</v>
       </c>
-      <c r="G4" s="2">
-        <v>3578.27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
-        <v>11.1</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2.4620000000000002</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
       <c r="D5" s="3">
         <v>28</v>
       </c>
@@ -666,20 +644,14 @@
       <c r="F5" s="2">
         <v>10.27</v>
       </c>
-      <c r="G5" s="2">
-        <v>6291.61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
-        <v>29.858000000000001</v>
-      </c>
-      <c r="C6" s="2">
-        <v>9.3699999999999992</v>
-      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
       <c r="D6" s="3">
         <v>24</v>
       </c>
@@ -689,20 +661,14 @@
       <c r="F6" s="2">
         <v>12.64</v>
       </c>
-      <c r="G6" s="3">
-        <v>17000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
-        <v>30.210999999999999</v>
-      </c>
-      <c r="C7" s="2">
-        <v>11.071999999999999</v>
-      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
       <c r="D7" s="3">
         <v>38</v>
       </c>
@@ -712,20 +678,14 @@
       <c r="F7" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G7" s="2">
-        <v>55080.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
-        <v>11.468</v>
-      </c>
-      <c r="C8" s="2">
-        <v>3.1179999999999999</v>
-      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
       <c r="D8" s="3">
         <v>26</v>
       </c>
@@ -735,20 +695,14 @@
       <c r="F8" s="2">
         <v>4.12</v>
       </c>
-      <c r="G8" s="2">
-        <v>3753.51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
-        <v>17.039000000000001</v>
-      </c>
-      <c r="C9" s="2">
-        <v>5.1909999999999998</v>
-      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
       <c r="D9" s="3">
         <v>29</v>
       </c>
@@ -758,20 +712,14 @@
       <c r="F9" s="2">
         <v>18.21</v>
       </c>
-      <c r="G9" s="2">
-        <v>17716.599999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2">
-        <v>8.1300000000000008</v>
-      </c>
-      <c r="C10" s="2">
-        <v>4.1180000000000003</v>
-      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
       <c r="D10" s="3">
         <v>31</v>
       </c>
@@ -781,20 +729,14 @@
       <c r="F10" s="2">
         <v>4.49</v>
       </c>
-      <c r="G10" s="2">
-        <v>38587.599999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
-        <v>4.6760000000000002</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2.8330000000000002</v>
-      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
       <c r="D11" s="3">
         <v>73</v>
       </c>
@@ -804,20 +746,14 @@
       <c r="F11" s="2">
         <v>-0.2</v>
       </c>
-      <c r="G11" s="2">
-        <v>574.54999999999995</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
-        <v>6.3920000000000003</v>
-      </c>
-      <c r="C12" s="2">
-        <v>3.4140000000000001</v>
-      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
       <c r="D12" s="3">
         <v>39</v>
       </c>
@@ -827,20 +763,14 @@
       <c r="F12" s="2">
         <v>21.76</v>
       </c>
-      <c r="G12" s="2">
-        <v>11516.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
-        <v>7.032</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1.9850000000000001</v>
-      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
       <c r="D13" s="3">
         <v>33</v>
       </c>
@@ -850,20 +780,14 @@
       <c r="F13" s="2">
         <v>2.2799999999999998</v>
       </c>
-      <c r="G13" s="2">
-        <v>9968.2800000000007</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2">
-        <v>18.870999999999999</v>
-      </c>
-      <c r="C14" s="2">
-        <v>6.0119999999999996</v>
-      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
       <c r="D14" s="3">
         <v>33</v>
       </c>
@@ -873,20 +797,14 @@
       <c r="F14" s="2">
         <v>4.8499999999999996</v>
       </c>
-      <c r="G14" s="2">
-        <v>1394.28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
-        <v>6.4210000000000003</v>
-      </c>
-      <c r="C15" s="2">
-        <v>1.306</v>
-      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
       <c r="D15" s="3">
         <v>39</v>
       </c>
@@ -896,20 +814,14 @@
       <c r="F15" s="2">
         <v>2.88</v>
       </c>
-      <c r="G15" s="2">
-        <v>1674.16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
-        <v>1.69</v>
-      </c>
-      <c r="C16" s="2">
-        <v>1.581</v>
-      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
       <c r="D16" s="3">
         <v>19</v>
       </c>
@@ -919,20 +831,14 @@
       <c r="F16" s="2">
         <v>27.79</v>
       </c>
-      <c r="G16" s="2">
-        <v>5886.94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
-        <v>25.279</v>
-      </c>
-      <c r="C17" s="2">
-        <v>12.244999999999999</v>
-      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
       <c r="D17" s="3">
         <v>38</v>
       </c>
@@ -942,20 +848,14 @@
       <c r="F17" s="2">
         <v>29.31</v>
       </c>
-      <c r="G17" s="2">
-        <v>1534.9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2">
-        <v>23.707999999999998</v>
-      </c>
-      <c r="C18" s="2">
-        <v>8.4459999999999997</v>
-      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
       <c r="D18" s="3">
         <v>25</v>
       </c>
@@ -965,20 +865,14 @@
       <c r="F18" s="2">
         <v>55.86</v>
       </c>
-      <c r="G18" s="2">
-        <v>2493.5700000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2">
-        <v>7.8639999999999999</v>
-      </c>
-      <c r="C19" s="2">
-        <v>3.6880000000000002</v>
-      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
       <c r="D19" s="3">
         <v>80</v>
       </c>
@@ -988,20 +882,14 @@
       <c r="F19" s="2">
         <v>2.7</v>
       </c>
-      <c r="G19" s="2">
-        <v>344.47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2">
-        <v>5.1639999999999997</v>
-      </c>
-      <c r="C20" s="2">
-        <v>0.82399999999999995</v>
-      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
       <c r="D20" s="3">
         <v>35</v>
       </c>
@@ -1011,20 +899,14 @@
       <c r="F20" s="2">
         <v>1.77</v>
       </c>
-      <c r="G20" s="2">
-        <v>3629.36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2">
-        <v>13.624000000000001</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3.214</v>
-      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
       <c r="D21" s="3">
         <v>78</v>
       </c>
@@ -1034,20 +916,14 @@
       <c r="F21" s="2">
         <v>0.71</v>
       </c>
-      <c r="G21" s="2">
-        <v>269.26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2">
-        <v>20.605</v>
-      </c>
-      <c r="C22" s="2">
-        <v>7.1920000000000002</v>
-      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
       <c r="D22" s="3">
         <v>71</v>
       </c>
@@ -1057,20 +933,14 @@
       <c r="F22" s="2">
         <v>1.22</v>
       </c>
-      <c r="G22" s="2">
-        <v>606.64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2">
-        <v>29.654</v>
-      </c>
-      <c r="C23" s="2">
-        <v>9.02</v>
-      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
       <c r="D23" s="3">
         <v>56</v>
       </c>
@@ -1080,20 +950,14 @@
       <c r="F23" s="2">
         <v>1.28</v>
       </c>
-      <c r="G23" s="2">
-        <v>274.73</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2">
-        <v>2.81</v>
-      </c>
-      <c r="C24" s="2">
-        <v>1.645</v>
-      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
       <c r="D24" s="3">
         <v>39</v>
       </c>
@@ -1103,20 +967,14 @@
       <c r="F24" s="2">
         <v>2.67</v>
       </c>
-      <c r="G24" s="2">
-        <v>4107.8500000000004</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2">
-        <v>65.218999999999994</v>
-      </c>
-      <c r="C25" s="2">
-        <v>32.494</v>
-      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
       <c r="D25" s="3">
         <v>44</v>
       </c>
@@ -1126,20 +984,14 @@
       <c r="F25" s="2">
         <v>4.6100000000000003</v>
       </c>
-      <c r="G25" s="2">
-        <v>20461.599999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2">
-        <v>4.88</v>
-      </c>
-      <c r="C26" s="2">
-        <v>0.27400000000000002</v>
-      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
       <c r="D26" s="3">
         <v>28</v>
       </c>
@@ -1149,20 +1001,14 @@
       <c r="F26" s="2">
         <v>19.52</v>
       </c>
-      <c r="G26" s="2">
-        <v>1066.01</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="2">
-        <v>12.425000000000001</v>
-      </c>
-      <c r="C27" s="2">
-        <v>5.1559999999999997</v>
-      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
       <c r="D27" s="3">
         <v>30</v>
       </c>
@@ -1172,20 +1018,14 @@
       <c r="F27" s="2">
         <v>4.33</v>
       </c>
-      <c r="G27" s="2">
-        <v>7883.96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="2">
-        <v>10.26</v>
-      </c>
-      <c r="C28" s="2">
-        <v>3.7629999999999999</v>
-      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
       <c r="D28" s="3">
         <v>62</v>
       </c>
@@ -1195,20 +1035,14 @@
       <c r="F28" s="2">
         <v>1.59</v>
       </c>
-      <c r="G28" s="2">
-        <v>501.44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="2">
-        <v>20.658000000000001</v>
-      </c>
-      <c r="C29" s="2">
-        <v>14.734</v>
-      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
       <c r="D29" s="3">
         <v>39</v>
       </c>
@@ -1218,20 +1052,14 @@
       <c r="F29" s="2">
         <v>7.8</v>
       </c>
-      <c r="G29" s="2">
-        <v>14054.9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="2">
-        <v>38.262999999999998</v>
-      </c>
-      <c r="C30" s="2">
-        <v>14.483000000000001</v>
-      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
       <c r="D30" s="3">
         <v>61</v>
       </c>
@@ -1241,20 +1069,14 @@
       <c r="F30" s="2">
         <v>2.56</v>
       </c>
-      <c r="G30" s="2">
-        <v>272.66000000000003</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="2">
-        <v>19.262</v>
-      </c>
-      <c r="C31" s="2">
-        <v>9.2550000000000008</v>
-      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
       <c r="D31" s="3">
         <v>32</v>
       </c>
@@ -1264,20 +1086,14 @@
       <c r="F31" s="2">
         <v>24.8</v>
       </c>
-      <c r="G31" s="2">
-        <v>3323.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="2">
-        <v>5.1539999999999999</v>
-      </c>
-      <c r="C32" s="2">
-        <v>1.7310000000000001</v>
-      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
       <c r="D32" s="3">
         <v>27</v>
       </c>
@@ -1287,20 +1103,14 @@
       <c r="F32" s="2">
         <v>2.5499999999999998</v>
       </c>
-      <c r="G32" s="2">
-        <v>5193.99</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="2">
-        <v>23.239000000000001</v>
-      </c>
-      <c r="C33" s="2">
-        <v>7.0759999999999996</v>
-      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
       <c r="D33" s="3">
         <v>38</v>
       </c>
@@ -1310,20 +1120,14 @@
       <c r="F33" s="2">
         <v>53.8</v>
       </c>
-      <c r="G33" s="2">
-        <v>2345.41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="2">
-        <v>16.911999999999999</v>
-      </c>
-      <c r="C34" s="2">
-        <v>5.625</v>
-      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
       <c r="D34" s="3">
         <v>33</v>
       </c>
@@ -1333,20 +1137,14 @@
       <c r="F34" s="2">
         <v>5.93</v>
       </c>
-      <c r="G34" s="2">
-        <v>517.15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="2">
-        <v>35.369999999999997</v>
-      </c>
-      <c r="C35" s="2">
-        <v>11.510999999999999</v>
-      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
       <c r="D35" s="3">
         <v>23</v>
       </c>
@@ -1356,20 +1154,14 @@
       <c r="F35" s="2">
         <v>38.9</v>
       </c>
-      <c r="G35" s="2">
-        <v>6980.7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="2">
-        <v>8.7840000000000007</v>
-      </c>
-      <c r="C36" s="2">
-        <v>4.8179999999999996</v>
-      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
       <c r="D36" s="3">
         <v>16</v>
       </c>
@@ -1379,20 +1171,14 @@
       <c r="F36" s="2">
         <v>2.84</v>
       </c>
-      <c r="G36" s="2">
-        <v>2344.9899999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="2">
-        <v>11.849</v>
-      </c>
-      <c r="C37" s="2">
-        <v>2.7690000000000001</v>
-      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
       <c r="D37" s="3">
         <v>56</v>
       </c>
@@ -1402,20 +1188,14 @@
       <c r="F37" s="2">
         <v>5.34</v>
       </c>
-      <c r="G37" s="2">
-        <v>582.52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="2">
-        <v>13.541</v>
-      </c>
-      <c r="C38" s="2">
-        <v>6.2060000000000004</v>
-      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
       <c r="D38" s="3">
         <v>74</v>
       </c>
@@ -1425,20 +1205,14 @@
       <c r="F38" s="2">
         <v>7.79</v>
       </c>
-      <c r="G38" s="2">
-        <v>633.76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="2">
-        <v>32.65</v>
-      </c>
-      <c r="C39" s="2">
-        <v>11.32</v>
-      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
       <c r="D39" s="3">
         <v>39</v>
       </c>
@@ -1448,20 +1222,14 @@
       <c r="F39" s="2">
         <v>2.42</v>
       </c>
-      <c r="G39" s="2">
-        <v>356.93</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="2">
-        <v>9.5210000000000008</v>
-      </c>
-      <c r="C40" s="2">
-        <v>4.4039999999999999</v>
-      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
       <c r="D40" s="3">
         <v>36</v>
       </c>
@@ -1471,20 +1239,14 @@
       <c r="F40" s="2">
         <v>10.06</v>
       </c>
-      <c r="G40" s="2">
-        <v>1260.8499999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="2">
-        <v>11.73</v>
-      </c>
-      <c r="C41" s="2">
-        <v>2.1</v>
-      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
       <c r="D41" s="3">
         <v>48</v>
       </c>
@@ -1494,20 +1256,14 @@
       <c r="F41" s="2">
         <v>5.68</v>
       </c>
-      <c r="G41" s="2">
-        <v>621.69000000000005</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G41" s="2"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="2">
-        <v>11.156000000000001</v>
-      </c>
-      <c r="C42" s="2">
-        <v>4.01</v>
-      </c>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
       <c r="D42" s="3">
         <v>73</v>
       </c>
@@ -1517,20 +1273,14 @@
       <c r="F42" s="2">
         <v>3.06</v>
       </c>
-      <c r="G42" s="2">
-        <v>272.74</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="2">
-        <v>25.884</v>
-      </c>
-      <c r="C43" s="2">
-        <v>3.4319999999999999</v>
-      </c>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
       <c r="D43" s="3">
         <v>37</v>
       </c>
@@ -1540,20 +1290,14 @@
       <c r="F43" s="2">
         <v>8.02</v>
       </c>
-      <c r="G43" s="2">
-        <v>313.66000000000003</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="G43" s="2"/>
+    </row>
+    <row r="44" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="2">
-        <v>8.5809999999999995</v>
-      </c>
-      <c r="C44" s="2">
-        <v>1.569</v>
-      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
       <c r="D44" s="3">
         <v>42</v>
       </c>
@@ -1563,20 +1307,14 @@
       <c r="F44" s="2">
         <v>0.11</v>
       </c>
-      <c r="G44" s="2">
-        <v>2075.67</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G44" s="2"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="2">
-        <v>4.8360000000000003</v>
-      </c>
-      <c r="C45" s="2">
-        <v>2.419</v>
-      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
       <c r="D45" s="3">
         <v>29</v>
       </c>
@@ -1586,9 +1324,7 @@
       <c r="F45" s="2">
         <v>3.83</v>
       </c>
-      <c r="G45" s="2">
-        <v>2511.65</v>
-      </c>
+      <c r="G45" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
